--- a/PMI-DZT2/ПМИ ТокЗ/pmi_tokzdzt/example.xlsx
+++ b/PMI-DZT2/ПМИ ТокЗ/pmi_tokzdzt/example.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d.sharygin\Desktop\pmi_devices\DZT2\PMI-DZT2\PMI-DZT2\ПМИ ТокЗ\pmi_tokzdzt\rtponn_modes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d.sharygin\Desktop\pmi_devices\DZT2\PMI-DZT2\PMI-DZT2\ПМИ ТокЗ\pmi_tokzdzt\rtpovn_modes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5214A5AF-C774-4237-8998-A3FA8E9364DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D03D157F-FC72-42B0-8CD1-0DC0C7CA1920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39285" yWindow="2535" windowWidth="28800" windowHeight="15345" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SGF_Parameters" sheetId="1" r:id="rId1"/>
@@ -57,9 +57,6 @@
     <t>IC1</t>
   </si>
   <si>
-    <t>OV_hvptoc1_strpalc</t>
-  </si>
-  <si>
     <t>pusk_ptrc1_tprmofflvlgc</t>
   </si>
   <si>
@@ -421,6 +418,9 @@
   </si>
   <si>
     <t>DZT2_LVALH_1_CALH1_Alarm</t>
+  </si>
+  <si>
+    <t>DI_STRTPALC_HVPTOC1</t>
   </si>
 </sst>
 </file>
@@ -817,52 +817,52 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>0</v>
@@ -960,49 +960,49 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -1109,73 +1109,73 @@
         <v>8</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="P1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="AC1" s="2" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
@@ -1279,208 +1279,208 @@
   <sheetData>
     <row r="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AD1" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AG1" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AH1" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AI1" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AK1" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AL1" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AM1" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AN1" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AO1" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AP1" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AR1" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AS1" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AT1" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="AT1" s="2" t="s">
+      <c r="AU1" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AV1" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AW1" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AX1" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AY1" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="AZ1" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="BA1" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="BB1" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="BC1" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="BC1" s="2" t="s">
+      <c r="BD1" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="BD1" s="2" t="s">
+      <c r="BE1" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="BE1" s="2" t="s">
+      <c r="BF1" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="BF1" s="2" t="s">
+      <c r="BG1" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="BG1" s="2" t="s">
+      <c r="BH1" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="BH1" s="2" t="s">
+      <c r="BI1" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="BI1" s="2" t="s">
+      <c r="BJ1" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="BJ1" s="2" t="s">
+      <c r="BK1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="BL1" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="BK1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="BL1" s="2" t="s">
+      <c r="BM1" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="BM1" s="2" t="s">
+      <c r="BN1" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="BN1" s="2" t="s">
+      <c r="BO1" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="BO1" s="2" t="s">
+      <c r="BP1" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="BP1" s="2" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:68" x14ac:dyDescent="0.25">
